--- a/pigx-upms/pigx-upms-biz/src/main/resources/file/qa.xlsx
+++ b/pigx-upms/pigx-upms-biz/src/main/resources/file/qa.xlsx
@@ -7,7 +7,7 @@
     <workbookView windowWidth="29100" windowHeight="14560"/>
   </bookViews>
   <sheets>
-    <sheet name="MaxKB产品介绍" sheetId="1" r:id="rId1"/>
+    <sheet name="pig" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
